--- a/workshop_prep/bob_item4_retail_expansion_backup.xlsx
+++ b/workshop_prep/bob_item4_retail_expansion_backup.xlsx
@@ -1,21 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Store Roster (from MTP slide)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Country Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Market Indicator - WS and Ecom" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Layer Mix by Market" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Austria Account Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="New-Store Account Codes (sales " sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Outlet Benchmark (Zalando-Stadi" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Outlet Supply Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Roster (from MTP slide)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Payback - Capex vs EBIT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vintage Cohort Check" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Country Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Indicator - WS and Ecom" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layer Mix by Market" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Austria Account Detail" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Germany Channel Divergence" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New-Store Account Codes (sales " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retail Channel Data Gap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outlet Benchmark (Zalando-Stadi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outlet Supply Summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -468,85 +472,646 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Country Summary</t>
+          <t>Store Payback - Capex vs EBIT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Store count, total indicative gross sales/EBIT/capex, rolled up by country</t>
+          <t>Every store ranked by Capex-to-EBIT payback (years) and ROIC, not Capex-to-Sales -- shows why Gross Sales alone would have missed Copenhagen entirely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Market Indicator - WS and Ecom</t>
+          <t>Vintage Cohort Check</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Existing Wholesale and E-com sales by target country (2024 vs 2025), used as a market-readiness indicator ahead of each store opening</t>
+          <t>Average EBIT margin and payback by store opening-year cohort -- confirms a 0.71 correlation between years-to-mature-by-2032 and EBIT margin, meaning the 2032 figures are a single calendar-year snapshot, not a normalized run-rate</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Layer Mix by Market</t>
+          <t>Country Summary</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Top 5 layers by sales share, Wholesale+E-com combined, for each target country -- 'what's selling' today</t>
+          <t>Store count, total indicative gross sales/EBIT/capex, rolled up by country</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria Account Detail</t>
+          <t>Market Indicator - WS and Ecom</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Full account-level detail for Austria -- the single largest country bet with the thinnest existing footprint</t>
+          <t>Existing Wholesale and E-com sales by target country (2024 vs 2025), used as a market-readiness indicator ahead of each store opening</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>New-Store Account Codes (sales system)</t>
+          <t>Layer Mix by Market</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The three store-type account codes found live in the sales system (Helsinki Brand Store, Helsinki Outlet Village, Intercompany NO OL Store) -- none show any recorded sales in FY24 or FY25, and none appear on the MTP store roster</t>
+          <t>Top 5 layers by sales share, Wholesale+E-com combined, for each target country -- 'what's selling' today</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Outlet Benchmark (Zalando-Stadium)</t>
+          <t>Austria Account Detail</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025 sales/units/GM% for the two existing 3rd-party outlet-type accounts (Zalando Lounge, Stadium Outlet) -- the benchmark for sizing new owned-outlet economics</t>
+          <t>Full account-level detail for Austria -- the single largest country bet with the thinnest existing footprint</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Germany Channel Divergence</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Germany, 2024 vs 2025, split three ways (Zalando/Independent Wholesale/Haglofs own E-com) -- shows growth concentrating in the discount channel while independent full-price accounts shrink</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>New-Store Account Codes (sales system)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The three store-type account codes found live in the sales system (Helsinki Brand Store, Helsinki Outlet Village, Intercompany NO OL Store) -- none show any recorded sales in FY24 or FY25, and none appear on the MTP store roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Retail Channel Data Gap</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Confirms 100% of Retail-channel sales sit under a generic customer-group code with no store-level identifier -- brand store and owned outlet sales cannot be split in this data</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Outlet Benchmark (Zalando-Stadium)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025 sales/units/GM% for the two existing 3rd-party outlet-type accounts (Zalando Lounge, Stadium Outlet) -- the benchmark for sizing new owned-outlet economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Outlet Supply Summary</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>SEK and unit sizing of the 'end of season / no confirmed FW27 continuation' product pool that would feed an owned-outlet strategy, vs. Harvest tier's YoY unit decline</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="n">
+        <v>114071256.3090572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>141574</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="n">
+        <v>123001879.3407176</v>
+      </c>
+      <c r="D3" t="n">
+        <v>149949</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HAGLÖFS BRAND STORE HELSINKI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HAGLÖFS BRAND STORE HELSINKI</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HELSINKI OUTLET VILLAGE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HELSINKI OUTLET VILLAGE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Customer Group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="n">
+        <v>114071256.3090572</v>
+      </c>
+      <c r="D2" t="n">
+        <v>141574</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>*BLANK*</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" t="n">
+        <v>123001879.3407176</v>
+      </c>
+      <c r="D3" t="n">
+        <v>149949</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HAGLÖFS BRAND STORE HELSINKI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HAGLÖFS BRAND STORE HELSINKI</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HELSINKI OUTLET VILLAGE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HELSINKI OUTLET VILLAGE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sales_2025</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Units_2025</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>GM%_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ZALANDO</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52597797.78</v>
+      </c>
+      <c r="C2" t="n">
+        <v>101259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3014292772544287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STADIUM Outlet</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9555692.76</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23887</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2601056995474183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sales_2025</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Units_2025</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Units_2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FW27 confirm-or-exit list (211 franchises)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>211</v>
+      </c>
+      <c r="C2" t="n">
+        <v>87346750.6592848</v>
+      </c>
+      <c r="D2" t="n">
+        <v>149855</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Harvest tier (total)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>236</v>
+      </c>
+      <c r="C3" t="n">
+        <v>120238785.4040606</v>
+      </c>
+      <c r="D3" t="n">
+        <v>183414</v>
+      </c>
+      <c r="E3" t="n">
+        <v>331320</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Problem Child tier (total)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>151</v>
+      </c>
+      <c r="C4" t="n">
+        <v>94768130.81872503</v>
+      </c>
+      <c r="D4" t="n">
+        <v>97929</v>
       </c>
     </row>
   </sheetData>
@@ -1116,6 +1681,916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sales_RR_MSEK</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>EBIT_RR_MSEK</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Capex_MSEK</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>YearsToMatureBy2032</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>EBIT_margin_pct</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CapexToSales_pct</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Payback_years</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ROIC_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Innsbruck</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L2" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>St Anton</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Outlet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pandorf (AT)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Munchen</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L6" t="n">
+        <v>59.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Outlet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Outlet UK</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L7" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Salzburg</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="L8" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Arlanda</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Emporia (Malmo)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L10" t="n">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L11" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gothenburg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vienna</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L13" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Brand Store</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>YearsToMatureBy2032</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AvgEBITmargin</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AvgPayback</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1272,7 +2747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1590,7 +3065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2172,7 +3647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2268,342 +3743,185 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Customer Group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>*BLANK*</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C2" t="n">
-        <v>114071256.3090572</v>
-      </c>
-      <c r="D2" t="n">
-        <v>141574</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>*BLANK*</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C3" t="n">
-        <v>123001879.3407176</v>
-      </c>
-      <c r="D3" t="n">
-        <v>149949</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HAGLÖFS BRAND STORE HELSINKI</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HAGLÖFS BRAND STORE HELSINKI</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>HELSINKI OUTLET VILLAGE</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>HELSINKI OUTLET VILLAGE</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INTERCOMPANY HAGLÖFS NO OL STORE</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Account</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sales_2025</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Units_2025</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>GM%_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ZALANDO</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>52597797.78</v>
-      </c>
-      <c r="C2" t="n">
-        <v>101259</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3014292772544287</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STADIUM Outlet</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>9555692.76</v>
-      </c>
-      <c r="C3" t="n">
-        <v>23887</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2601056995474183</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Channel</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Sales_2025</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Units_2025</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Units_2024</t>
+          <t>ASP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GM%</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FW27 confirm-or-exit list (211 franchises)</t>
+          <t>Haglofs own E-com</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>211</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="n">
-        <v>87346750.6592848</v>
+        <v>11535066.03</v>
       </c>
       <c r="D2" t="n">
-        <v>149855</v>
+        <v>8490</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1358.665021201413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6827232102112206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Harvest tier (total)</t>
+          <t>Haglofs own E-com</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>236</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>120238785.4040606</v>
+        <v>15076444.59</v>
       </c>
       <c r="D3" t="n">
-        <v>183414</v>
+        <v>11959</v>
       </c>
       <c r="E3" t="n">
-        <v>331320</v>
+        <v>1260.677697968058</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6406401670063777</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Problem Child tier (total)</t>
+          <t>Independent Wholesale (ex-Zalando)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>151</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>94768130.81872503</v>
+        <v>37578175.55</v>
       </c>
       <c r="D4" t="n">
-        <v>97929</v>
+        <v>50482</v>
+      </c>
+      <c r="E4" t="n">
+        <v>744.3876143972109</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4339827011638941</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Independent Wholesale (ex-Zalando)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30720900.61</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40899</v>
+      </c>
+      <c r="E5" t="n">
+        <v>751.1406295997457</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4372585403836571</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Zalando (discount)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34573420.99</v>
+      </c>
+      <c r="D6" t="n">
+        <v>73834</v>
+      </c>
+      <c r="E6" t="n">
+        <v>468.258810168757</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.359614979483695</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Zalando (discount)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="n">
+        <v>52531715.85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>101211</v>
+      </c>
+      <c r="E7" t="n">
+        <v>519.031684797107</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3009526609628153</v>
       </c>
     </row>
   </sheetData>

--- a/workshop_prep/bob_item4_retail_expansion_backup.xlsx
+++ b/workshop_prep/bob_item4_retail_expansion_backup.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retail Channel Data Gap" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outlet Benchmark (Zalando-Stadi" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outlet Supply Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YTD2026 Germany &amp; Austria" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1119,6 +1120,195 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>FY2025_SEK</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>YTD2026_SEK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FY2025_Units</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>YTD2026_Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zalando</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>52531715.85</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20854009</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Germany Wholesale</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Independent Wholesale ex-Zalando</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30720900.61</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16163149</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Germany Wholesale</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total German Wholesale</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>83252616.45999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>37017158</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Germany Wholesale</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Austria, all channels</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wholesale</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Austria, all channels</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>926670.26</v>
+      </c>
+      <c r="C7" t="n">
+        <v>464610.43</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Austria, all channels</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>E-com</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>606</v>
+      </c>
+      <c r="G7" t="n">
+        <v>390</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
